--- a/BWI/bestwine_output/bestwine_Virgin Islands British.xlsx
+++ b/BWI/bestwine_output/bestwine_Virgin Islands British.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA8"/>
+  <dimension ref="A1:AA9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1270,6 +1270,87 @@
       <c r="Z8" s="3" t="inlineStr"/>
       <c r="AA8" s="3" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Botella Bvi</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Botella Bvi</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>121880</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Virgin Islands (British)</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Road Town</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Tortola</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Building 1, Tortola Pier Park</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.botellabvi.com</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>contact@botellabvi.com</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/botellabvi/</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/botellabvi</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr"/>
+      <c r="V9" s="2" t="inlineStr"/>
+      <c r="W9" s="2" t="inlineStr"/>
+      <c r="X9" s="2" t="inlineStr"/>
+      <c r="Y9" s="2" t="inlineStr"/>
+      <c r="Z9" s="2" t="inlineStr"/>
+      <c r="AA9" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
